--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.38681</v>
+        <v>16.44106</v>
       </c>
       <c r="D2" t="n">
-        <v>16.53652</v>
+        <v>16.24486</v>
       </c>
       <c r="E2" t="n">
-        <v>16.46864</v>
+        <v>16.43462</v>
       </c>
       <c r="F2" t="n">
-        <v>42.30028</v>
+        <v>41.76896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04992</v>
+        <v>0.0493</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79801</v>
+        <v>1.8028</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.47382</v>
+        <v>16.55459</v>
       </c>
       <c r="D3" t="n">
-        <v>16.32432</v>
+        <v>16.21142</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58004</v>
+        <v>16.28104</v>
       </c>
       <c r="F3" t="n">
-        <v>42.36214</v>
+        <v>42.36788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05054</v>
+        <v>0.05033</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77467</v>
+        <v>1.80175</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.62664</v>
+        <v>16.72464</v>
       </c>
       <c r="D4" t="n">
-        <v>16.53461</v>
+        <v>16.14806</v>
       </c>
       <c r="E4" t="n">
-        <v>16.52018</v>
+        <v>16.3676</v>
       </c>
       <c r="F4" t="n">
-        <v>41.4305</v>
+        <v>42.30177</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04978</v>
+        <v>0.05053</v>
       </c>
       <c r="H4" t="n">
-        <v>1.805</v>
+        <v>1.78244</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.49755</v>
+        <v>16.57799</v>
       </c>
       <c r="D5" t="n">
-        <v>16.26155</v>
+        <v>16.1851</v>
       </c>
       <c r="E5" t="n">
-        <v>16.51624</v>
+        <v>16.46771</v>
       </c>
       <c r="F5" t="n">
-        <v>41.65124</v>
+        <v>42.44326</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04906</v>
+        <v>0.05068</v>
       </c>
       <c r="H5" t="n">
-        <v>1.77488</v>
+        <v>1.78481</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.52796</v>
+        <v>16.56438</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37049</v>
+        <v>16.07222</v>
       </c>
       <c r="E6" t="n">
-        <v>16.21489</v>
+        <v>16.11373</v>
       </c>
       <c r="F6" t="n">
-        <v>41.83479</v>
+        <v>41.6154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05032</v>
+        <v>0.0513</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81528</v>
+        <v>1.81412</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.43034</v>
+        <v>16.55831</v>
       </c>
       <c r="D7" t="n">
-        <v>16.43721</v>
+        <v>16.31833</v>
       </c>
       <c r="E7" t="n">
-        <v>16.43307</v>
+        <v>16.50661</v>
       </c>
       <c r="F7" t="n">
-        <v>42.65225</v>
+        <v>41.85458</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05023</v>
+        <v>0.04912</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80133</v>
+        <v>1.77966</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.47266</v>
+        <v>16.7445</v>
       </c>
       <c r="D8" t="n">
-        <v>16.79193</v>
+        <v>16.52439</v>
       </c>
       <c r="E8" t="n">
-        <v>16.42822</v>
+        <v>16.57111</v>
       </c>
       <c r="F8" t="n">
-        <v>42.12221</v>
+        <v>41.8089</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05</v>
+        <v>0.0506</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80075</v>
+        <v>1.83661</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.62401</v>
+        <v>17.23677</v>
       </c>
       <c r="D9" t="n">
-        <v>16.32197</v>
+        <v>16.25981</v>
       </c>
       <c r="E9" t="n">
-        <v>16.31618</v>
+        <v>16.47607</v>
       </c>
       <c r="F9" t="n">
-        <v>42.16993</v>
+        <v>41.9529</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05033</v>
+        <v>0.04917</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82011</v>
+        <v>1.80734</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.45485</v>
+        <v>16.86454</v>
       </c>
       <c r="D10" t="n">
-        <v>16.32286</v>
+        <v>16.4741</v>
       </c>
       <c r="E10" t="n">
-        <v>16.84563</v>
+        <v>16.54399</v>
       </c>
       <c r="F10" t="n">
-        <v>42.06229</v>
+        <v>41.86269</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05049</v>
+        <v>0.05097</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8158</v>
+        <v>1.79529</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60216</v>
+        <v>0.59803</v>
       </c>
       <c r="D12" t="n">
-        <v>1.06251</v>
+        <v>1.06222</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.58562</v>
+        <v>0.59904</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09783</v>
+        <v>1.09517</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59756</v>
+        <v>0.59279</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09014</v>
+        <v>1.09427</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59336</v>
+        <v>0.59349</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09108</v>
+        <v>1.1066</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.59396</v>
+        <v>0.58955</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11636</v>
+        <v>1.10234</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61072</v>
+        <v>0.6029600000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09984</v>
+        <v>1.08575</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5992499999999999</v>
+        <v>0.5920299999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1.09889</v>
+        <v>1.10545</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.59742</v>
+        <v>0.60425</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12009</v>
+        <v>1.10984</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.61008</v>
+        <v>0.5955</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09845</v>
+        <v>1.09152</v>
       </c>
     </row>
   </sheetData>
